--- a/Documentacion/Documentacion_Fuente_Multisalida.xlsx
+++ b/Documentacion/Documentacion_Fuente_Multisalida.xlsx
@@ -16,33 +16,21 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="438">
-  <si>
-    <t>Restricciones de diseño</t>
-  </si>
-  <si>
-    <t>Requerimientos funcionales — lo mínimo que necesita el proyecto para funcionar</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="393">
   <si>
     <t>Requerimientos no funcionales</t>
   </si>
   <si>
-    <t>Restricciones que condicionan la solución antes de diseñar. Celdas en amarillo: completar por el grupo.</t>
-  </si>
-  <si>
-    <t>Valores numéricos tomados de la hoja 'Cálculos' (supuestos editables). Prioridad: Esencial = sin esto la fuente no cumple la especificación; Deseable = mejora recomendada.</t>
-  </si>
-  <si>
-    <t>Describen cómo debe ser el sistema (calidad, estética, seguridad, fabricación). Celdas en amarillo: completar por el grupo.</t>
+    <t xml:space="preserve">Requerimientos funcionales </t>
   </si>
   <si>
     <t>Especificaciones del proyecto — Fuente de alimentación multisalida para laboratorio</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>Restricciones de diseño</t>
   </si>
   <si>
-    <t>1. Información general</t>
+    <t>ID</t>
   </si>
   <si>
     <t>Requerimiento</t>
@@ -51,64 +39,103 @@
     <t>Descripción / criterio</t>
   </si>
   <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Categoría</t>
+  </si>
+  <si>
     <t>Prioridad</t>
+  </si>
+  <si>
+    <t>Restricción</t>
   </si>
   <si>
     <t>Verificación</t>
   </si>
   <si>
-    <t>RF-01</t>
+    <t>Impacto</t>
   </si>
   <si>
-    <t>Tipo</t>
+    <t>Criterio / verificación</t>
   </si>
   <si>
-    <t>Restricción</t>
-  </si>
-  <si>
-    <t>Impacto</t>
+    <t>1. Información general</t>
   </si>
   <si>
     <t>Mitigación / decisión</t>
   </si>
   <si>
-    <t>Alimentación de entrada</t>
+    <t>RF-01</t>
   </si>
   <si>
     <t>RD-01</t>
   </si>
   <si>
+    <t>RNF-01</t>
+  </si>
+  <si>
+    <t>Alimentación de entrada</t>
+  </si>
+  <si>
+    <t>Estética</t>
+  </si>
+  <si>
+    <t>Fabricación</t>
+  </si>
+  <si>
     <t>Transformador AC de laboratorio con secundario de 24 Vac y potencia ≥ 353 VA (incluye margen del 20%). Si el transformador disponible es menor, se debe limitar la carga total simultánea.</t>
+  </si>
+  <si>
+    <t>Disposición ordenada de bornes y controles; serigrafía legible con nombre de rieles y polaridad; bornes con código de colores consistente; acabado limpio de la PCB y del montaje.</t>
   </si>
   <si>
     <t>Esencial</t>
   </si>
   <si>
-    <t>Fabricación</t>
+    <t>Revisión visual por el grupo y docente</t>
+  </si>
+  <si>
+    <t>PCB fabricada por termotransferencia: anchos de pista y separaciones mínimas limitados (propuesto ≥ 0.5 mm en pistas de potencia y ≥ 0.4 mm de separación), sin vías metalizadas.</t>
   </si>
   <si>
     <t>Medir tensión del secundario; revisar placa de características</t>
   </si>
   <si>
+    <t>Deseable</t>
+  </si>
+  <si>
+    <t>Limita el uso de SMD pequeños y de doble cara.</t>
+  </si>
+  <si>
     <t>RF-02</t>
   </si>
   <si>
-    <t>PCB fabricada por termotransferencia: anchos de pista y separaciones mínimas limitados (propuesto ≥ 0.5 mm en pistas de potencia y ≥ 0.4 mm de separación), sin vías metalizadas.</t>
+    <t>Usar through-hole o SMD de paso amplio (TO-220, TO-263, SOIC); puentes con cable o remaches en lugar de vías.</t>
   </si>
   <si>
     <t>Protección y encendido de entrada</t>
   </si>
   <si>
-    <t>Limita el uso de SMD pequeños y de doble cara.</t>
+    <t>RNF-02</t>
+  </si>
+  <si>
+    <t>Tamaño</t>
   </si>
   <si>
     <t>Interruptor general (≥ 250 VAC) y fusible retardado en el primario (≥ 4.4 A, valor comercial superior). Cableado de red fuera de la PCB.</t>
   </si>
   <si>
-    <t>Usar through-hole o SMD de paso amplio (TO-220, TO-263, SOIC); puentes con cable o remaches en lugar de vías.</t>
+    <t>RD-02</t>
+  </si>
+  <si>
+    <t>Corriente en pistas</t>
   </si>
   <si>
     <t>Inspección y prueba de continuidad</t>
+  </si>
+  <si>
+    <t>Dimensiones de la PCB compatibles con la placa virgen disponible y con la caja/montaje. Dimensión máxima: [completar].</t>
   </si>
   <si>
     <t>RF-03</t>
@@ -117,25 +144,22 @@
     <t>Rectificación</t>
   </si>
   <si>
-    <t>RD-02</t>
+    <t>Pistas de 5 A y bus de ~7 A con cobre de 1 oz exigen anchos de varios milímetros.</t>
   </si>
   <si>
     <t>Puente de diodos de onda completa con corriente ≥ 14 A (2× la corriente DC del bus) y tensión inversa ≥ 100 V, con disipador.</t>
   </si>
   <si>
-    <t>Corriente en pistas</t>
+    <t>Proyecto</t>
   </si>
   <si>
     <t>Medir tensión DC tras el puente</t>
   </si>
   <si>
-    <t>Pistas de 5 A y bus de ~7 A con cobre de 1 oz exigen anchos de varios milímetros (ver hoja 'Cálculos').</t>
-  </si>
-  <si>
     <t>RF-04</t>
   </si>
   <si>
-    <t>Proyecto</t>
+    <t>Medir PCB terminada</t>
   </si>
   <si>
     <t>Filtrado capacitivo</t>
@@ -150,7 +174,7 @@
     <t>Pistas anchas, refuerzo con estaño o cable, planos de cobre amplios; reducir lazos de potencia.</t>
   </si>
   <si>
-    <t>Categoría</t>
+    <t>RNF-03</t>
   </si>
   <si>
     <t>Fuente de alimentación multisalida para laboratorio</t>
@@ -162,34 +186,49 @@
     <t>RD-03</t>
   </si>
   <si>
-    <t>RF-05</t>
+    <t>Costo</t>
   </si>
   <si>
     <t>Entrada</t>
   </si>
   <si>
+    <t>RF-05</t>
+  </si>
+  <si>
+    <t>Presupuesto máximo: [completar]. Preferir componentes comerciales de fácil consecución.</t>
+  </si>
+  <si>
     <t>Bus de alimentación VIN DC</t>
+  </si>
+  <si>
+    <t>BOM con costos</t>
   </si>
   <si>
     <t>Asignatura / programa</t>
   </si>
   <si>
-    <t>Bus DC entre 26 V (carga plena, red baja) y 37 V (sin carga, red alta), que alimenta todos los convertidores. Ancho de pista según hoja 'Cálculos'.</t>
+    <t>La entrada es un transformador AC de laboratorio de potencia limitada. Se requieren ≥ 353 VA para todas las salidas a plena carga simultánea.</t>
   </si>
   <si>
-    <t>Criterio / verificación</t>
-  </si>
-  <si>
-    <t>La entrada es un transformador AC de laboratorio de potencia limitada. Se requieren ≥ 353 VA para todas las salidas a plena carga simultánea.</t>
+    <t>Bus DC entre 26 V (carga plena, red baja) y 37 V (sin carga, red alta), que alimenta todos los convertidores. Ancho de pista según hoja 'Cálculos'.</t>
   </si>
   <si>
     <t>Diseño y prototipado electronico  — Ingeniería Mecatrónica, 2026-2</t>
   </si>
   <si>
+    <t>Si el transformador es menor, no se puede usar toda la potencia a la vez.</t>
+  </si>
+  <si>
     <t>Medir VIN en vacío y con carga</t>
   </si>
   <si>
-    <t>Si el transformador es menor, no se puede usar toda la potencia a la vez.</t>
+    <t>RNF-04</t>
+  </si>
+  <si>
+    <t>Confirmar datos del transformador; si es necesario, limitar corriente total o reducir salidas simultáneas.</t>
+  </si>
+  <si>
+    <t>Eficiencia</t>
   </si>
   <si>
     <t>RF-06</t>
@@ -198,103 +237,139 @@
     <t>Salida +12 V / 5 A</t>
   </si>
   <si>
-    <t>Confirmar datos del transformador; si es necesario, limitar corriente total o reducir salidas simultáneas.</t>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>RD-04</t>
+  </si>
+  <si>
+    <t>Eficiencia global ≥ 80 % a plena carga (la hoja 'Cálculos' estima ~85 % con los supuestos actuales).</t>
   </si>
   <si>
     <t>Convertidor Buck (reductor) dimensionado para ≥ 6 A (5 A + 20 % de margen).</t>
   </si>
   <si>
-    <t>Objetivo</t>
+    <t>Rango de tensión del bus</t>
+  </si>
+  <si>
+    <t>Diseñar, fabricar y validar una fuente de alimentación de múltiples salidas (+12 V, +5 V, +3.3 V, −12 V y una salida variable) para alimentar proyectos electrónicos de laboratorio.</t>
+  </si>
+  <si>
+    <t>Medir potencia de entrada vs. salida</t>
   </si>
   <si>
     <t>Carga de 5 A, medir tensión y temperatura</t>
   </si>
   <si>
-    <t>RD-04</t>
-  </si>
-  <si>
-    <t>Diseñar, fabricar y validar una fuente de alimentación de múltiples salidas (+12 V, +5 V, +3.3 V, −12 V y una salida variable) para alimentar proyectos electrónicos de laboratorio.</t>
+    <t>El bus DC varía entre ~26 V y ~37 V. Los CI convertidores deben soportar ≥ 40 V de entrada (el inversor, ≥ 49 V entre pines).</t>
   </si>
   <si>
     <t>RF-07</t>
   </si>
   <si>
-    <t>Rango de tensión del bus</t>
+    <t>Reduce los CI candidatos.</t>
+  </si>
+  <si>
+    <t>RNF-05</t>
   </si>
   <si>
     <t>Salida +5 V / 5 A</t>
   </si>
   <si>
-    <t>El bus DC varía entre ~26 V y ~37 V. Los CI convertidores deben soportar ≥ 40 V de entrada (el inversor, ≥ 49 V entre pines).</t>
+    <t>Alcance</t>
   </si>
   <si>
-    <t>Alcance</t>
+    <t>Seleccionar CI de 40 V (o versión HV de 60 V para el inversor).</t>
+  </si>
+  <si>
+    <t>Gestión térmica</t>
   </si>
   <si>
     <t>Captura esquemática (Altium Designer), diseño de PCB y fabricación mediante termotransferencia; conversión DC/DC integrada en la PCB.</t>
   </si>
   <si>
-    <t>Reduce los CI candidatos.</t>
+    <t>RD-05</t>
   </si>
   <si>
-    <t>RNF-01</t>
+    <t>Temperatura de disipadores ≤ 70 °C a plena carga con ambiente de 25 °C (valor propuesto). Disipadores y, si es necesario, ventilador.</t>
+  </si>
+  <si>
+    <t>Disipación térmica</t>
+  </si>
+  <si>
+    <t>Termómetro / termopar tras 1 h a plena carga</t>
   </si>
   <si>
     <t>RF-08</t>
   </si>
   <si>
-    <t>Seleccionar CI de 40 V (o versión HV de 60 V para el inversor).</t>
+    <t>Nombre</t>
+  </si>
+  <si>
+    <t>Con eficiencias estimadas se disipan ~27 W a plena carga.</t>
   </si>
   <si>
     <t>Salida +3.3 V / 3 A</t>
   </si>
   <si>
-    <t>Nombre</t>
+    <t>Requiere disipadores y espacio de ventilación.</t>
   </si>
   <si>
     <t>Convertidor Buck (reductor) dimensionado para ≥ 3.6 A (3 A + 20 % de margen).</t>
   </si>
   <si>
-    <t>Estética</t>
+    <t>Yeison Eduardo Gonzalez</t>
   </si>
   <si>
-    <t>RD-05</t>
+    <t>RNF-06</t>
+  </si>
+  <si>
+    <t>Disipadores en puente y convertidores, ventilador opcional, separar fuentes de calor.</t>
+  </si>
+  <si>
+    <t>Confiabilidad</t>
   </si>
   <si>
     <t>Carga de 3 A, medir tensión y temperatura</t>
   </si>
   <si>
+    <t>RD-06</t>
+  </si>
+  <si>
+    <t>Operación continua a plena carga durante ≥ 1 h sin falla ni disparo de protecciones.</t>
+  </si>
+  <si>
     <t>RF-09</t>
   </si>
   <si>
-    <t>Disposición ordenada de bornes y controles; serigrafía legible con nombre de rieles y polaridad; bornes con código de colores consistente; acabado limpio de la PCB y del montaje.</t>
+    <t>Margen de diseño</t>
   </si>
   <si>
-    <t>Disipación térmica</t>
-  </si>
-  <si>
-    <t>Yeison Eduardo Gonzalez</t>
+    <t>Prueba de estrés</t>
   </si>
   <si>
     <t>Salida −12 V / 1 A</t>
   </si>
   <si>
-    <t>Revisión visual por el grupo y docente</t>
+    <t>Dimensionar con margen de seguridad de 20–30 % sobre la corriente máxima (se usa 20 %).</t>
   </si>
   <si>
     <t>Convertidor inversor (Buck-Boost inversor) para ≥ 1.2 A; la tensión negativa comparte la referencia GND común.</t>
   </si>
   <si>
-    <t>Con eficiencias estimadas se disipan ~27 W a plena carga.</t>
+    <t>Los CI de 5 A no alcanzan para las salidas de 5 A.</t>
+  </si>
+  <si>
+    <t>RNF-07</t>
   </si>
   <si>
     <t>Carga de 1 A, medir polaridad y tensión</t>
   </si>
   <si>
-    <t>Deseable</t>
+    <t>Usar CI de ≥ 8 A en +12 V y +5 V.</t>
   </si>
   <si>
-    <t>Requiere disipadores y espacio de ventilación.</t>
+    <t>Seguridad eléctrica</t>
   </si>
   <si>
     <t>RF-10</t>
@@ -303,13 +378,13 @@
     <t>Salida variable 1.25–15 V / 3 A</t>
   </si>
   <si>
-    <t>Disipadores en puente y convertidores, ventilador opcional, separar fuentes de calor.</t>
+    <t>La tensión de red solo llega al interruptor, fusible y transformador (fuera de la PCB); la PCB trabaja con baja tensión. Zonas con tensión de red aisladas y cubiertas.</t>
   </si>
   <si>
-    <t>RNF-02</t>
+    <t>RD-07</t>
   </si>
   <si>
-    <t>RD-06</t>
+    <t>Inspección antes de energizar</t>
   </si>
   <si>
     <t>Convertidor Buck ajustable con potenciómetro multivuelta, dimensionado para ≥ 3.6 A (3 A + 20 % de margen). Se descarta regulador lineal por disipación excesiva.</t>
@@ -318,91 +393,121 @@
     <t>Versión / fecha</t>
   </si>
   <si>
-    <t>Margen de diseño</t>
+    <t>Seguridad</t>
   </si>
   <si>
-    <t>Tamaño</t>
+    <t>v0.1 — 01/10/2026</t>
   </si>
   <si>
     <t>Barrido de tensión y carga de 3 A</t>
   </si>
   <si>
-    <t>v0.1 — 01/10/2026</t>
+    <t>Se trabaja con red de 120 VAC en el primario del transformador.</t>
   </si>
   <si>
-    <t>Dimensionar con margen de seguridad de 20–30 % sobre la corriente máxima (se usa 20 %).</t>
+    <t>RNF-08</t>
+  </si>
+  <si>
+    <t>La parte de red debe quedar fuera de la PCB.</t>
   </si>
   <si>
     <t>RF-11</t>
   </si>
   <si>
+    <t>Calidad de salida</t>
+  </si>
+  <si>
+    <t>Fusible, interruptor y cableado de red aislados; energizar solo tras inspección.</t>
+  </si>
+  <si>
     <t>Referencia común (GND)</t>
   </si>
   <si>
-    <t>Los CI de 5 A no alcanzan para las salidas de 5 A.</t>
+    <t>Rizado ≤ 100 mVpp y exactitud ± 5 % en todas las salidas (valores propuestos).</t>
   </si>
   <si>
     <t>Todas las salidas comparten un GND común; GND de potencia y de señal unidos en un solo punto.</t>
   </si>
   <si>
-    <t>Usar CI de ≥ 8 A en +12 V y +5 V.</t>
+    <t>RD-08</t>
+  </si>
+  <si>
+    <t>Osciloscopio y multímetro</t>
   </si>
   <si>
     <t>Continuidad entre bornes GND</t>
   </si>
   <si>
-    <t>Dimensiones de la PCB compatibles con la placa virgen disponible y con la caja/montaje. Dimensión máxima: [completar].</t>
-  </si>
-  <si>
-    <t>RD-07</t>
+    <t>Disponibilidad de componentes</t>
   </si>
   <si>
     <t>RF-12</t>
   </si>
   <si>
-    <t>Seguridad</t>
+    <t>Componentes disponibles en tiendas nacionales (I+D Electrónica, Sigma Electrónica, Vistronica, Ferretrónica) o importables (Digi-Key, Mouser, LCSC, Octopart).</t>
+  </si>
+  <si>
+    <t>RNF-09</t>
+  </si>
+  <si>
+    <t>2. Entrada de la fuente</t>
   </si>
   <si>
     <t>Protección de salidas</t>
   </si>
   <si>
-    <t>Se trabaja con red de 120 VAC en el primario del transformador.</t>
+    <t>Compatibilidad EMI</t>
+  </si>
+  <si>
+    <t>Tiempos de entrega e importación.</t>
   </si>
   <si>
     <t>Limitación de corriente y protección térmica del CI convertidor, más fusible o PTC por salida. Protección contra sobretensión (TVS/zener) en los rieles sensibles (3.3 V).</t>
   </si>
   <si>
-    <t>La parte de red debe quedar fuera de la PCB.</t>
+    <t>Lazos de conmutación cortos, separación entre sección de potencia y salidas, plano/pista de GND amplia.</t>
+  </si>
+  <si>
+    <t>Verificar existencias antes de fijar la lista; tener alternativa por bloque.</t>
+  </si>
+  <si>
+    <t>Revisión de layout</t>
   </si>
   <si>
     <t>Prueba de cortocircuito controlada</t>
   </si>
   <si>
-    <t>Fusible, interruptor y cableado de red aislados; energizar solo tras inspección.</t>
+    <t>RD-09</t>
+  </si>
+  <si>
+    <t>Presupuesto</t>
   </si>
   <si>
     <t>RF-13</t>
   </si>
   <si>
+    <t>RNF-10</t>
+  </si>
+  <si>
     <t>Conectores de salida</t>
   </si>
   <si>
-    <t>RD-08</t>
+    <t>Manufacturabilidad</t>
   </si>
   <si>
     <t>Bornes con capacidad ≥ 6 A, identificados por riel (+12 V, +5 V, +3.3 V, −12 V, VAR, GND).</t>
   </si>
   <si>
-    <t>Disponibilidad de componentes</t>
+    <t>Presupuesto disponible: [completar].</t>
   </si>
   <si>
-    <t>Componentes disponibles en tiendas nacionales (I+D Electrónica, Sigma Electrónica, Vistronica, Ferretrónica) o importables (Digi-Key, Mouser, LCSC, Octopart).</t>
+    <t>Diseño compatible con termotransferencia: componentes through-hole o SMD de paso amplio, pistas y separaciones según hoja 'Restricciones'.</t>
   </si>
   <si>
-    <t>2. Entrada de la fuente</t>
+    <t>Revisión DRC en Altium y prueba de transferencia</t>
   </si>
   <si>
-    <t>Tiempos de entrega e importación.</t>
+    <t>Condiciona selección de componentes y conectores.</t>
   </si>
   <si>
     <t>RF-14</t>
@@ -411,22 +516,34 @@
     <t>Indicación de estado</t>
   </si>
   <si>
-    <t>Verificar existencias antes de fijar la lista; tener alternativa por bloque.</t>
+    <t>Registrar costo por componente en la BOM.</t>
+  </si>
+  <si>
+    <t>Etapa</t>
+  </si>
+  <si>
+    <t>RNF-11</t>
   </si>
   <si>
     <t>LED indicador por cada riel de salida.</t>
   </si>
   <si>
-    <t>RD-09</t>
+    <t>RD-10</t>
+  </si>
+  <si>
+    <t>Mantenibilidad</t>
+  </si>
+  <si>
+    <t>Descripción</t>
   </si>
   <si>
     <t>Inspección visual</t>
   </si>
   <si>
-    <t>Medir PCB terminada</t>
+    <t>Fusibles reemplazables, componentes de potencia accesibles, designadores claros en serigrafía.</t>
   </si>
   <si>
-    <t>Presupuesto</t>
+    <t>Inspección</t>
   </si>
   <si>
     <t>RF-15</t>
@@ -438,109 +555,70 @@
     <t>Punto de prueba para VIN DC y para cada salida.</t>
   </si>
   <si>
-    <t>Presupuesto disponible: [completar].</t>
+    <t>RNF-12</t>
   </si>
   <si>
-    <t>RNF-03</t>
+    <t>Documentación</t>
+  </si>
+  <si>
+    <t>Esquemáticos, diagrama de bloques, árbol de potencia, BOM y datasheets organizados en el repositorio git (Documentation/Datasheets).</t>
   </si>
   <si>
     <t>RF-16</t>
   </si>
   <si>
-    <t>Condiciona selección de componentes y conectores.</t>
-  </si>
-  <si>
     <t>Lectura de la salida variable</t>
   </si>
   <si>
-    <t>Costo</t>
+    <t>Revisión del repositorio</t>
   </si>
   <si>
-    <t>Etapa</t>
-  </si>
-  <si>
-    <t>Registrar costo por componente en la BOM.</t>
+    <t>Tiempo</t>
   </si>
   <si>
     <t>Voltímetro de panel o display para la salida variable.</t>
   </si>
   <si>
-    <t>Presupuesto máximo: [completar]. Preferir componentes comerciales de fácil consecución.</t>
-  </si>
-  <si>
-    <t>RD-10</t>
+    <t>Fecha de entrega / cronograma: [completar].</t>
   </si>
   <si>
     <t>Comparar con multímetro</t>
   </si>
   <si>
-    <t>Descripción</t>
-  </si>
-  <si>
-    <t>BOM con costos</t>
-  </si>
-  <si>
-    <t>Tiempo</t>
-  </si>
-  <si>
-    <t>Fecha de entrega / cronograma: [completar].</t>
-  </si>
-  <si>
-    <t>RNF-04</t>
-  </si>
-  <si>
-    <t>Eficiencia</t>
+    <t>RNF-13</t>
   </si>
   <si>
     <t>Limita iteraciones de PCB.</t>
   </si>
   <si>
-    <t>Eficiencia global ≥ 80 % a plena carga (la hoja 'Cálculos' estima ~85 % con los supuestos actuales).</t>
-  </si>
-  <si>
-    <t>Medir potencia de entrada vs. salida</t>
-  </si>
-  <si>
-    <t>RNF-05</t>
-  </si>
-  <si>
-    <t>Gestión térmica</t>
-  </si>
-  <si>
-    <t>Temperatura de disipadores ≤ 70 °C a plena carga con ambiente de 25 °C (valor propuesto). Disipadores y, si es necesario, ventilador.</t>
+    <t>Usabilidad</t>
   </si>
   <si>
     <t>Planificar una sola iteración de PCB con revisión previa.</t>
   </si>
   <si>
-    <t>Termómetro / termopar tras 1 h a plena carga</t>
+    <t>Salida variable fácil de ajustar y de leer; rieles identificados para evitar conexiones erróneas.</t>
+  </si>
+  <si>
+    <t>Fuente primaria</t>
+  </si>
+  <si>
+    <t>Prueba de uso</t>
   </si>
   <si>
     <t>RD-11</t>
   </si>
   <si>
-    <t>Fuente primaria</t>
-  </si>
-  <si>
-    <t>RNF-06</t>
-  </si>
-  <si>
     <t>Espacio y mecánica</t>
   </si>
   <si>
-    <t>Confiabilidad</t>
+    <t>Transformador AC del laboratorio</t>
   </si>
   <si>
     <t>Dimensiones de PCB, caja y montaje de conectores: [completar].</t>
   </si>
   <si>
-    <t>Operación continua a plena carga durante ≥ 1 h sin falla ni disparo de protecciones.</t>
-  </si>
-  <si>
     <t>Condiciona colocación de bornes y disipadores.</t>
-  </si>
-  <si>
-    <t>Prueba de estrés</t>
   </si>
   <si>
     <t>Definir la caja antes del layout.</t>
@@ -552,25 +630,13 @@
     <t>Temperatura de operación</t>
   </si>
   <si>
-    <t>Transformador AC del laboratorio</t>
-  </si>
-  <si>
-    <t>RNF-07</t>
-  </si>
-  <si>
     <t>Operación en ambiente de laboratorio (propuesto 15–35 °C).</t>
   </si>
   <si>
     <t>Define el derating térmico.</t>
   </si>
   <si>
-    <t>Seguridad eléctrica</t>
-  </si>
-  <si>
     <t>Seleccionar componentes con rango comercial o superior.</t>
-  </si>
-  <si>
-    <t>La tensión de red solo llega al interruptor, fusible y transformador (fuera de la PCB); la PCB trabaja con baja tensión. Zonas con tensión de red aisladas y cubiertas.</t>
   </si>
   <si>
     <t>RD-13</t>
@@ -579,7 +645,7 @@
     <t>Herramientas y organización</t>
   </si>
   <si>
-    <t>Inspección antes de energizar</t>
+    <t>Puente de diodos</t>
   </si>
   <si>
     <t>Diseño en Altium Designer; proyecto en repositorio git con carpetas Documentación, PCB/Altium 'Trunk' y Librerías de Altium.</t>
@@ -591,13 +657,7 @@
     <t>Crear el repositorio y la estructura antes de iniciar el esquemático.</t>
   </si>
   <si>
-    <t>RNF-08</t>
-  </si>
-  <si>
     <t>RD-14</t>
-  </si>
-  <si>
-    <t>Calidad de salida</t>
   </si>
   <si>
     <t>Costo, volumen y manufactura (DFM)</t>
@@ -606,88 +666,19 @@
     <t>Prototipo único; el diseño debe ser fabricable con los medios del laboratorio.</t>
   </si>
   <si>
-    <t>Rizado ≤ 100 mVpp y exactitud ± 5 % en todas las salidas (valores propuestos).</t>
-  </si>
-  <si>
     <t>Evita componentes que requieran reflow o equipos especiales.</t>
   </si>
   <si>
     <t>Revisión DFM antes de imprimir la PCB.</t>
   </si>
   <si>
-    <t>Osciloscopio y multímetro</t>
-  </si>
-  <si>
-    <t>RNF-09</t>
-  </si>
-  <si>
-    <t>Compatibilidad EMI</t>
-  </si>
-  <si>
-    <t>Lazos de conmutación cortos, separación entre sección de potencia y salidas, plano/pista de GND amplia.</t>
-  </si>
-  <si>
-    <t>Revisión de layout</t>
-  </si>
-  <si>
-    <t>Puente de diodos</t>
-  </si>
-  <si>
-    <t>RNF-10</t>
-  </si>
-  <si>
-    <t>Manufacturabilidad</t>
-  </si>
-  <si>
-    <t>Diseño compatible con termotransferencia: componentes through-hole o SMD de paso amplio, pistas y separaciones según hoja 'Restricciones'.</t>
-  </si>
-  <si>
-    <t>Revisión DRC en Altium y prueba de transferencia</t>
-  </si>
-  <si>
     <t>Filtrado</t>
-  </si>
-  <si>
-    <t>RNF-11</t>
-  </si>
-  <si>
-    <t>Mantenibilidad</t>
-  </si>
-  <si>
-    <t>Fusibles reemplazables, componentes de potencia accesibles, designadores claros en serigrafía.</t>
-  </si>
-  <si>
-    <t>Inspección</t>
-  </si>
-  <si>
-    <t>RNF-12</t>
-  </si>
-  <si>
-    <t>Documentación</t>
-  </si>
-  <si>
-    <t>Esquemáticos, diagrama de bloques, árbol de potencia, BOM y datasheets organizados en el repositorio git (Documentation/Datasheets).</t>
-  </si>
-  <si>
-    <t>Revisión del repositorio</t>
   </si>
   <si>
     <t>Conversión</t>
   </si>
   <si>
     <t>Conversión DC/DC integrada en la PCB</t>
-  </si>
-  <si>
-    <t>RNF-13</t>
-  </si>
-  <si>
-    <t>Usabilidad</t>
-  </si>
-  <si>
-    <t>Salida variable fácil de ajustar y de leer; rieles identificados para evitar conexiones erróneas.</t>
-  </si>
-  <si>
-    <t>Prueba de uso</t>
   </si>
   <si>
     <t>3. Salidas de la fuente</t>
@@ -738,70 +729,7 @@
     <t>Potencia total de salida (todas a plena carga)</t>
   </si>
   <si>
-    <t>Nota: la salida variable se calcula con 15 V (valor máximo).</t>
-  </si>
-  <si>
-    <t>4. Criterios de aceptación / validación (propuestos — ajustar con el docente)</t>
-  </si>
-  <si>
-    <t>Parámetro</t>
-  </si>
-  <si>
-    <t>Meta</t>
-  </si>
-  <si>
-    <t>Método de verificación</t>
-  </si>
-  <si>
-    <t>Exactitud de tensión de salida</t>
-  </si>
-  <si>
-    <t>± 5 % del nominal</t>
-  </si>
-  <si>
-    <t>Multímetro, sin carga y a plena carga</t>
-  </si>
-  <si>
-    <t>Rizado y ruido</t>
-  </si>
-  <si>
-    <t>≤ 100 mVpp a plena carga</t>
-  </si>
-  <si>
-    <t>Osciloscopio, acople AC, ancho de banda limitado a 20 MHz</t>
-  </si>
-  <si>
-    <t>Regulación de carga</t>
-  </si>
-  <si>
-    <t>≤ 2 %</t>
-  </si>
-  <si>
-    <t>Medir con carga de 0 % y 100 % de la corriente máxima</t>
-  </si>
-  <si>
-    <t>Prueba a plena carga</t>
-  </si>
-  <si>
-    <t>≥ 1 h sin falla</t>
-  </si>
-  <si>
-    <t>Cargas resistivas / electrónicas por riel, medir temperatura de disipadores</t>
-  </si>
-  <si>
-    <t>Rango de la salida variable</t>
-  </si>
-  <si>
-    <t>1.25 V a 15 V</t>
-  </si>
-  <si>
-    <t>Barrer el potenciómetro y registrar tensión mínima y máxima</t>
-  </si>
-  <si>
     <t>Lista preliminar de componentes principales</t>
-  </si>
-  <si>
-    <t>Candidatos PRELIMINARES: cada uno debe validarse con su datasheet (guardar en Documentation/Datasheets) y justificarse antes de congelar el diseño. Búsqueda: Digi-Key, Mouser, LCSC, Octopart; local: I+D Electrónica, Sigma Electrónica, Vistronica, Ferretrónica.</t>
   </si>
   <si>
     <t>#</t>
@@ -858,21 +786,6 @@
     <t>Valor comercial superior al mínimo calculado.</t>
   </si>
   <si>
-    <t>Protección contra sobretensión de red</t>
-  </si>
-  <si>
-    <t>Varistor (MOV) 130–150 VAC</t>
-  </si>
-  <si>
-    <t>Radial</t>
-  </si>
-  <si>
-    <t>Absorbe picos de la red en el primario.</t>
-  </si>
-  <si>
-    <t>Opcional (deseable).</t>
-  </si>
-  <si>
     <t>Transformador de entrada</t>
   </si>
   <si>
@@ -894,9 +807,6 @@
     <t>Puente rectificador</t>
   </si>
   <si>
-    <t>Cálculos de soporte — presupuesto de potencia y dimensionamiento</t>
-  </si>
-  <si>
     <t>KBPC1510 o equivalente (15 A, 1000 V)</t>
   </si>
   <si>
@@ -910,9 +820,6 @@
   </si>
   <si>
     <t>Capacitores de filtrado</t>
-  </si>
-  <si>
-    <t>Celdas con texto azul = supuestos editables; el resto son fórmulas. Todos los supuestos son propuestos por el grupo y deben validarse con los datasheets.</t>
   </si>
   <si>
     <t>4 × 4700 µF / 50 V electrolíticos de bajo ESR</t>
@@ -960,9 +867,6 @@
     <t>Por validar con datasheet</t>
   </si>
   <si>
-    <t>A. Supuestos (editar)</t>
-  </si>
-  <si>
     <t>Convertidor Buck +5 V</t>
   </si>
   <si>
@@ -973,12 +877,6 @@
   </si>
   <si>
     <t>Convertidor Buck +3.3 V</t>
-  </si>
-  <si>
-    <t>LM2678T-ADJ o LM2678T-3.3 (5 A, 40 V)</t>
-  </si>
-  <si>
-    <t>TO-220-7</t>
   </si>
   <si>
     <t>5 A cubre 3 A + margen; encapsulado through-hole.</t>
@@ -996,9 +894,6 @@
     <t>TO-263-5 / TO-220-5</t>
   </si>
   <si>
-    <t>Tensión del secundario del transformador (Vac rms)</t>
-  </si>
-  <si>
     <t>Versión HV soporta la tensión del bus más 12 V entre pines.</t>
   </si>
   <si>
@@ -1009,6 +904,9 @@
   </si>
   <si>
     <t>LM2678T-ADJ + potenciómetro multivuelta 10 kΩ</t>
+  </si>
+  <si>
+    <t>TO-220-7</t>
   </si>
   <si>
     <t>Salida ajustable desde ~1.2 V; 5 A cubre 3 A + margen.</t>
@@ -1035,12 +933,6 @@
     <t>Por calcular</t>
   </si>
   <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>Propuesto; confirmar con transformador del laboratorio</t>
-  </si>
-  <si>
     <t>Diodos Schottky de recirculación</t>
   </si>
   <si>
@@ -1056,19 +948,10 @@
     <t>Verificar tensión inversa ≥ 49 V en el inversor.</t>
   </si>
   <si>
-    <t>Frecuencia de red</t>
-  </si>
-  <si>
     <t>Capacitores de entrada/salida de convertidores</t>
   </si>
   <si>
-    <t>Hz</t>
-  </si>
-  <si>
     <t>Electrolíticos bajo ESR 25–50 V + cerámicos 100 nF</t>
-  </si>
-  <si>
-    <t>Red en Colombia: 60 Hz</t>
   </si>
   <si>
     <t>Radial / 0805</t>
@@ -1080,16 +963,10 @@
     <t>Valores según datasheet de cada CI.</t>
   </si>
   <si>
-    <t>Tensión nominal de red</t>
-  </si>
-  <si>
     <t>Protección de salida</t>
   </si>
   <si>
     <t>Fusible o PTC por salida (≈ 6.3 A en +12/+5 V, 4 A en +3.3 V y variable, 1.6 A en −12 V) y TVS en el riel de 3.3 V</t>
-  </si>
-  <si>
-    <t>Red monofásica en Colombia: 120 V</t>
   </si>
   <si>
     <t>Portafusible / SMD</t>
@@ -1099,9 +976,6 @@
   </si>
   <si>
     <t>Ajustar valores tras validar corrientes de diseño.</t>
-  </si>
-  <si>
-    <t>Tolerancia alta combinada (red + regulación en vacío)</t>
   </si>
   <si>
     <t>Bornes de panel (tipo banana) ≥ 10 A, uno por riel + GND</t>
@@ -1116,9 +990,6 @@
     <t>Código de colores por riel.</t>
   </si>
   <si>
-    <t>Supuesto del grupo</t>
-  </si>
-  <si>
     <t>Conectores de PCB</t>
   </si>
   <si>
@@ -1131,58 +1002,52 @@
     <t>Verificar paso y corriente.</t>
   </si>
   <si>
-    <t>Tolerancia baja de red</t>
+    <t>Cálculos de soporte — presupuesto de potencia y dimensionamiento</t>
   </si>
   <si>
-    <t>Indicadores LED</t>
+    <t>A. Supuestos (editar)</t>
   </si>
   <si>
-    <t>LED 3 mm/5 mm + resistencia limitadora por riel</t>
+    <t>Tensión del secundario del transformador (Vac rms)</t>
   </si>
   <si>
-    <t>Indicación de presencia de cada tensión.</t>
+    <t>V</t>
   </si>
   <si>
-    <t>Calcular resistencia por riel.</t>
+    <t>Propuesto; confirmar con transformador del laboratorio</t>
+  </si>
+  <si>
+    <t>Frecuencia de red</t>
+  </si>
+  <si>
+    <t>Hz</t>
+  </si>
+  <si>
+    <t>Red en Colombia: 60 Hz</t>
+  </si>
+  <si>
+    <t>Tensión nominal de red</t>
+  </si>
+  <si>
+    <t>Red monofásica en Colombia: 120 V</t>
+  </si>
+  <si>
+    <t>Tolerancia alta combinada (red + regulación en vacío)</t>
+  </si>
+  <si>
+    <t>Supuesto del grupo</t>
+  </si>
+  <si>
+    <t>Tolerancia baja de red</t>
   </si>
   <si>
     <t>Caída por diodo del puente</t>
   </si>
   <si>
-    <t>Disipadores y ventilación</t>
-  </si>
-  <si>
     <t>Valor típico; confirmar en datasheet</t>
   </si>
   <si>
-    <t>Disipadores para puente y CI TO-220/TO-263; ventilador de 12 V opcional</t>
-  </si>
-  <si>
-    <t>Chasis / PCB</t>
-  </si>
-  <si>
-    <t>Se disipan ~27 W a plena carga.</t>
-  </si>
-  <si>
-    <t>Dimensionar con la resistencia térmica del datasheet.</t>
-  </si>
-  <si>
     <t>Rizado pico a pico permitido en el bus</t>
-  </si>
-  <si>
-    <t>Visualización (opcional)</t>
-  </si>
-  <si>
-    <t>Voltímetro de panel DC para la salida variable</t>
-  </si>
-  <si>
-    <t>Lectura directa de la tensión ajustada.</t>
-  </si>
-  <si>
-    <t>Deseable.</t>
-  </si>
-  <si>
-    <t>Opcional</t>
   </si>
   <si>
     <t>Factor corriente RMS secundario / corriente DC</t>
@@ -1340,7 +1205,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1354,15 +1219,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <sz val="9.0"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -1371,14 +1236,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FF3B3F58"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font/>
@@ -1395,8 +1260,14 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1405,7 +1276,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1428,12 +1299,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1501,57 +1366,63 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="7" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1563,31 +1434,43 @@
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="5" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="11" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="12" numFmtId="9" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
@@ -1851,12 +1734,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
+      <c r="A1" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2"/>
+      <c r="A2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="3"/>
@@ -1866,63 +1749,63 @@
       <c r="E3" s="3"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="8"/>
+      <c r="A4" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" ht="18.0" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>45</v>
+      <c r="A5" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="18.0" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>55</v>
+      <c r="A6" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>65</v>
+      <c r="A7" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>71</v>
+      <c r="A8" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="9" ht="18.0" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="8"/>
+      <c r="A9" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" ht="18.0" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>103</v>
+      <c r="A10" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="11">
@@ -1933,68 +1816,68 @@
       <c r="E11" s="3"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
+      <c r="A12" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" ht="30.0" customHeight="1">
-      <c r="A13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="17"/>
+      <c r="A13" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="19"/>
     </row>
     <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>178</v>
-      </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="17"/>
+      <c r="A14" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="19"/>
     </row>
     <row r="15" ht="18.0" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
+      <c r="A15" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="20" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="19"/>
     </row>
     <row r="16" ht="18.0" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
+      <c r="A16" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="19"/>
     </row>
     <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" s="18" t="s">
+      <c r="A17" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
+      <c r="B17" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="19"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -2004,134 +1887,132 @@
       <c r="E18" s="3"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="9"/>
+    </row>
+    <row r="20" ht="30.0" customHeight="1">
+      <c r="A20" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-    </row>
-    <row r="20" ht="30.0" customHeight="1">
-      <c r="A20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="C20" s="4" t="s">
+    </row>
+    <row r="21" ht="18.0" customHeight="1">
+      <c r="A21" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" ht="18.0" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B21" s="5">
+      <c r="B21" s="6">
         <v>12.0</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <v>5.0</v>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="21">
         <f t="shared" ref="D21:D24" si="1">ABS(B21)*C21</f>
         <v>60</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>231</v>
+      <c r="E21" s="6" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="22" ht="18.0" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="B22" s="5">
+      <c r="A22" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" s="6">
         <v>5.0</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <v>5.0</v>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="21">
         <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>231</v>
+      <c r="E22" s="6" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="23" ht="18.0" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B23" s="5">
+      <c r="A23" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B23" s="6">
         <v>3.3</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
         <v>3.0</v>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="21">
         <f t="shared" si="1"/>
         <v>9.9</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="24" ht="18.0" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="24" ht="18.0" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B24" s="5">
+      <c r="B24" s="6">
         <v>-12.0</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <v>1.0</v>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="21">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>235</v>
+      <c r="E24" s="6" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="25" ht="18.0" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>236</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="C25" s="5">
+      <c r="A25" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C25" s="6">
         <v>3.0</v>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="21">
         <f>15*C25</f>
         <v>45</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>238</v>
+      <c r="E25" s="6" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="20" t="s">
-        <v>239</v>
+      <c r="A26" s="22" t="s">
+        <v>236</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
-      <c r="D26" s="21">
+      <c r="D26" s="23">
         <f>SUM(D21:D25)</f>
         <v>151.9</v>
       </c>
-      <c r="E26" s="22" t="s">
-        <v>240</v>
-      </c>
+      <c r="E26" s="24"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
@@ -2141,91 +2022,53 @@
       <c r="E27" s="3"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="9"/>
     </row>
     <row r="29" ht="30.0" customHeight="1">
-      <c r="A29" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="4" t="s">
-        <v>244</v>
-      </c>
+      <c r="A29" s="26"/>
+      <c r="B29" s="27"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="26"/>
     </row>
     <row r="30" ht="18.0" customHeight="1">
-      <c r="A30" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B30" s="18" t="s">
-        <v>246</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="5" t="s">
-        <v>247</v>
-      </c>
+      <c r="A30" s="28"/>
+      <c r="B30" s="29"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="28"/>
     </row>
     <row r="31" ht="30.75" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B31" s="18" t="s">
-        <v>249</v>
-      </c>
-      <c r="C31" s="16"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="5" t="s">
-        <v>250</v>
-      </c>
+      <c r="A31" s="28"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="18"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="28"/>
     </row>
     <row r="32" ht="18.0" customHeight="1">
-      <c r="A32" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B32" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="5" t="s">
-        <v>253</v>
-      </c>
+      <c r="A32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="28"/>
     </row>
     <row r="33" ht="30.75" customHeight="1">
-      <c r="A33" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B33" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="5" t="s">
-        <v>256</v>
-      </c>
+      <c r="A33" s="28"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="28"/>
     </row>
     <row r="34" ht="30.75" customHeight="1">
-      <c r="A34" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B34" s="18" t="s">
-        <v>258</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="5" t="s">
-        <v>259</v>
-      </c>
+      <c r="A34" s="28"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="28"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
@@ -9042,306 +8885,308 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+    <row r="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" ht="30.0" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="B3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>12</v>
+    </row>
+    <row r="4" ht="44.25" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="44.25" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="A5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="E5" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" ht="44.25" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" ht="44.25" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" ht="30.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" ht="30.75" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" ht="30.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="12" ht="30.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" ht="44.25" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" ht="44.25" customHeight="1">
+      <c r="A15" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="16" ht="30.75" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" ht="18.0" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="D17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" ht="44.25" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" ht="44.25" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" ht="44.25" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" ht="44.25" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>30</v>
+      <c r="E17" s="6" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="18" ht="18.0" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" ht="18.0" customHeight="1">
-      <c r="A19" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="20" ht="30.75" customHeight="1">
-      <c r="A20" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>151</v>
-      </c>
+      <c r="A18" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="19" ht="30.75" customHeight="1">
+      <c r="A19" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="3"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
@@ -16196,17 +16041,9 @@
       <c r="D999" s="3"/>
       <c r="E999" s="3"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-      <c r="E1000" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -16231,259 +16068,261 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" ht="30.0" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" ht="44.25" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="5" t="s">
+    </row>
+    <row r="4" ht="44.25" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" ht="30.75" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="30.75" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" ht="30.75" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="E7" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" ht="44.25" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="D8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" ht="30.75" customHeight="1">
+      <c r="A9" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="5" t="s">
+      <c r="B9" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" ht="44.25" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" ht="30.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C7" s="14" t="s">
+      <c r="D11" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" ht="30.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="D12" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" ht="44.25" customHeight="1">
+      <c r="A13" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="9" ht="44.25" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="B13" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="E13" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D10" s="5" t="s">
+      <c r="B14" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="44.25" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="D14" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" ht="44.25" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B15" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="E15" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" ht="30.75" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="14" ht="44.25" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="16" ht="44.25" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>214</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" ht="30.75" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="D16" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3"/>
@@ -16499,7 +16338,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -23359,17 +23198,9 @@
       <c r="D999" s="3"/>
       <c r="E999" s="3"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-      <c r="E1000" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -23393,276 +23224,278 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+    </row>
+    <row r="3" ht="30.0" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="4" t="s">
+    </row>
+    <row r="4" ht="57.75" customHeight="1">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" ht="57.75" customHeight="1">
-      <c r="A5" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>29</v>
       </c>
+      <c r="E4" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="6" ht="44.25" customHeight="1">
-      <c r="A6" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>43</v>
+      <c r="A6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="7" ht="44.25" customHeight="1">
-      <c r="A7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" ht="44.25" customHeight="1">
-      <c r="A8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>75</v>
+      <c r="A7" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="8" ht="30.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>95</v>
+      <c r="A9" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="12" ht="57.75" customHeight="1">
-      <c r="A12" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="A10" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="D12" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" ht="18.0" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="D10" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C13" s="14" t="s">
+    </row>
+    <row r="11" ht="57.75" customHeight="1">
+      <c r="A11" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C11" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>147</v>
       </c>
+      <c r="E11" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="12" ht="18.0" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="13" ht="30.75" customHeight="1">
+      <c r="A13" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>164</v>
+      <c r="A14" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="17" ht="44.25" customHeight="1">
-      <c r="A17" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="18" ht="30.75" customHeight="1">
-      <c r="A18" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>198</v>
-      </c>
+      <c r="A15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" ht="44.25" customHeight="1">
+      <c r="A16" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="17" ht="30.75" customHeight="1">
+      <c r="A17" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3"/>
@@ -23671,7 +23504,7 @@
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -30531,17 +30364,9 @@
       <c r="D999" s="3"/>
       <c r="E999" s="3"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-      <c r="E1000" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -30568,529 +30393,477 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" ht="30.0" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" ht="30.75" customHeight="1">
+      <c r="A4" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" ht="44.25" customHeight="1">
+      <c r="A5" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" ht="44.25" customHeight="1">
+      <c r="A6" s="12">
+        <v>3.0</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="G6" s="6" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="7" ht="44.25" customHeight="1">
+      <c r="A7" s="12">
+        <v>4.0</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E7" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F7" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G7" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" ht="30.75" customHeight="1">
+      <c r="A8" s="12">
+        <v>5.0</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="5" ht="30.75" customHeight="1">
-      <c r="A5" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="B5" s="5" t="s">
+      <c r="D8" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="E8" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="G8" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="9" ht="30.75" customHeight="1">
+      <c r="A9" s="12">
+        <v>6.0</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="C9" s="6" t="s">
         <v>273</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="D9" s="6" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="6" ht="44.25" customHeight="1">
-      <c r="A6" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="E9" s="6" t="s">
         <v>275</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="F9" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="G9" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" ht="44.25" customHeight="1">
+      <c r="A10" s="12">
+        <v>7.0</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="C10" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="D10" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="B7" s="5" t="s">
+      <c r="E10" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="F10" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="G10" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="E7" s="5" t="s">
+    </row>
+    <row r="11" ht="30.75" customHeight="1">
+      <c r="A11" s="12">
+        <v>8.0</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="C11" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="E11" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="8" ht="44.25" customHeight="1">
-      <c r="A8" s="5">
-        <v>4.0</v>
-      </c>
-      <c r="B8" s="5" t="s">
+      <c r="F11" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="G11" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="12" ht="30.75" customHeight="1">
+      <c r="A12" s="12">
+        <v>9.0</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="C12" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F12" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="G12" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="13" ht="30.75" customHeight="1">
+      <c r="A13" s="12">
+        <v>10.0</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="C13" s="6" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="9" ht="44.25" customHeight="1">
-      <c r="A9" s="5">
-        <v>5.0</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="D13" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E13" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="G13" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="12">
+        <v>11.0</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="C14" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="D14" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="5">
-        <v>6.0</v>
-      </c>
-      <c r="B10" s="5" t="s">
+      <c r="E14" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="F14" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="15" ht="57.75" customHeight="1">
+      <c r="A15" s="12">
+        <v>12.0</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="C15" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="D15" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="E15" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="5">
-        <v>7.0</v>
-      </c>
-      <c r="B11" s="5" t="s">
+      <c r="F15" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="G15" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="D11" s="5" t="s">
+    </row>
+    <row r="16" ht="57.75" customHeight="1">
+      <c r="A16" s="12">
+        <v>13.0</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="C16" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="D16" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="12" ht="44.25" customHeight="1">
-      <c r="A12" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="B12" s="5" t="s">
+      <c r="E16" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="F16" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="G16" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17" ht="38.25" customHeight="1">
+      <c r="A17" s="12">
+        <v>14.0</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="C17" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="D17" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="E17" s="6" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="5">
-        <v>9.0</v>
-      </c>
-      <c r="B13" s="5" t="s">
+      <c r="F17" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="18" ht="57.75" customHeight="1">
+      <c r="A18" s="12">
+        <v>15.0</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C13" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="C18" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="D18" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="5">
-        <v>10.0</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="E18" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="F18" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="G18" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="19" ht="30.75" customHeight="1">
+      <c r="A19" s="12">
+        <v>16.0</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C19" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="D19" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="E19" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="5">
-        <v>11.0</v>
-      </c>
-      <c r="B15" s="5" t="s">
+      <c r="F19" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="G19" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="20" ht="30.75" customHeight="1">
+      <c r="A20" s="12">
+        <v>17.0</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="C20" s="6" t="s">
         <v>325</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="D20" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="F15" s="5" t="s">
-        <v>328</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="16" ht="30.75" customHeight="1">
-      <c r="A16" s="5">
-        <v>12.0</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>329</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>331</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="17" ht="57.75" customHeight="1">
-      <c r="A17" s="5">
-        <v>13.0</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>334</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="18" ht="57.75" customHeight="1">
-      <c r="A18" s="5">
-        <v>14.0</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>341</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>345</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="19" ht="30.75" customHeight="1">
-      <c r="A19" s="5">
-        <v>15.0</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>347</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="20" ht="57.75" customHeight="1">
-      <c r="A20" s="5">
-        <v>16.0</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>360</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" ht="30.75" customHeight="1">
-      <c r="A21" s="5">
-        <v>17.0</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>362</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>365</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="22" ht="30.75" customHeight="1">
-      <c r="A22" s="5">
-        <v>18.0</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>367</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>368</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="23" ht="30.75" customHeight="1">
-      <c r="A23" s="5">
-        <v>19.0</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>373</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>335</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="24" ht="44.25" customHeight="1">
-      <c r="A24" s="5">
-        <v>20.0</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>377</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>379</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>380</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>382</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="25" ht="30.75" customHeight="1">
-      <c r="A25" s="5">
-        <v>21.0</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>384</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>386</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>388</v>
-      </c>
+      <c r="G20" s="6" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
@@ -39822,55 +39595,9 @@
       <c r="F995" s="3"/>
       <c r="G995" s="3"/>
     </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="3"/>
-      <c r="B996" s="3"/>
-      <c r="C996" s="3"/>
-      <c r="D996" s="3"/>
-      <c r="E996" s="3"/>
-      <c r="F996" s="3"/>
-      <c r="G996" s="3"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="3"/>
-      <c r="B997" s="3"/>
-      <c r="C997" s="3"/>
-      <c r="D997" s="3"/>
-      <c r="E997" s="3"/>
-      <c r="F997" s="3"/>
-      <c r="G997" s="3"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="3"/>
-      <c r="B998" s="3"/>
-      <c r="C998" s="3"/>
-      <c r="D998" s="3"/>
-      <c r="E998" s="3"/>
-      <c r="F998" s="3"/>
-      <c r="G998" s="3"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="3"/>
-      <c r="B999" s="3"/>
-      <c r="C999" s="3"/>
-      <c r="D999" s="3"/>
-      <c r="E999" s="3"/>
-      <c r="F999" s="3"/>
-      <c r="G999" s="3"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-      <c r="E1000" s="3"/>
-      <c r="F1000" s="3"/>
-      <c r="G1000" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -39895,53 +39622,68 @@
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="2" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
+      <c r="A1" s="2" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" ht="15.0" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
-      <c r="A4" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="8"/>
+      <c r="A4" s="30" t="s">
+        <v>330</v>
+      </c>
+      <c r="B4" s="31">
+        <v>24.0</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>332</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="B5" s="24">
-        <v>24.0</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>340</v>
+      <c r="A5" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="B5" s="31">
+        <v>60.0</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>334</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>335</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
@@ -39951,17 +39693,17 @@
       <c r="J5" s="3"/>
     </row>
     <row r="6" ht="15.0" customHeight="1">
-      <c r="A6" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="B6" s="24">
-        <v>60.0</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>350</v>
+      <c r="A6" s="30" t="s">
+        <v>336</v>
+      </c>
+      <c r="B6" s="31">
+        <v>120.0</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>337</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
@@ -39971,17 +39713,15 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" ht="15.0" customHeight="1">
-      <c r="A7" s="23" t="s">
-        <v>354</v>
-      </c>
-      <c r="B7" s="24">
-        <v>120.0</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="A7" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="B7" s="32">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="30"/>
+      <c r="D7" s="24" t="s">
         <v>339</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>357</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -39991,15 +39731,15 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" ht="15.0" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="B8" s="25">
-        <v>0.15</v>
-      </c>
-      <c r="C8" s="23"/>
-      <c r="D8" s="22" t="s">
-        <v>366</v>
+      <c r="A8" s="30" t="s">
+        <v>340</v>
+      </c>
+      <c r="B8" s="32">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="30"/>
+      <c r="D8" s="24" t="s">
+        <v>339</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
@@ -40009,15 +39749,17 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" ht="15.0" customHeight="1">
-      <c r="A9" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="B9" s="25">
-        <v>0.1</v>
-      </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="22" t="s">
-        <v>366</v>
+      <c r="A9" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B9" s="31">
+        <v>1.1</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>342</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
@@ -40027,17 +39769,17 @@
       <c r="J9" s="3"/>
     </row>
     <row r="10" ht="15.0" customHeight="1">
-      <c r="A10" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="B10" s="24">
-        <v>1.1</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="A10" s="30" t="s">
+        <v>343</v>
+      </c>
+      <c r="B10" s="31">
+        <v>4.0</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D10" s="24" t="s">
         <v>339</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>378</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
@@ -40047,17 +39789,15 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" ht="15.0" customHeight="1">
-      <c r="A11" s="23" t="s">
-        <v>383</v>
-      </c>
-      <c r="B11" s="24">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D11" s="22" t="s">
-        <v>366</v>
+      <c r="A11" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B11" s="31">
+        <v>1.8</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="24" t="s">
+        <v>345</v>
       </c>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
@@ -40067,15 +39807,15 @@
       <c r="J11" s="3"/>
     </row>
     <row r="12" ht="15.0" customHeight="1">
-      <c r="A12" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="B12" s="24">
-        <v>1.8</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="22" t="s">
-        <v>390</v>
+      <c r="A12" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="B12" s="32">
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="24" t="s">
+        <v>347</v>
       </c>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
@@ -40085,15 +39825,17 @@
       <c r="J12" s="3"/>
     </row>
     <row r="13" ht="15.0" customHeight="1">
-      <c r="A13" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="B13" s="25">
-        <v>0.2</v>
-      </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="22" t="s">
-        <v>392</v>
+      <c r="A13" s="30" t="s">
+        <v>348</v>
+      </c>
+      <c r="B13" s="31">
+        <v>1.0</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>349</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>350</v>
       </c>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
@@ -40103,17 +39845,17 @@
       <c r="J13" s="3"/>
     </row>
     <row r="14" ht="15.0" customHeight="1">
-      <c r="A14" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="B14" s="24">
-        <v>1.0</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>394</v>
-      </c>
-      <c r="D14" s="22" t="s">
-        <v>395</v>
+      <c r="A14" s="30" t="s">
+        <v>351</v>
+      </c>
+      <c r="B14" s="31">
+        <v>10.0</v>
+      </c>
+      <c r="C14" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -40123,17 +39865,17 @@
       <c r="J14" s="3"/>
     </row>
     <row r="15" ht="15.0" customHeight="1">
-      <c r="A15" s="23" t="s">
-        <v>396</v>
-      </c>
-      <c r="B15" s="24">
-        <v>10.0</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>397</v>
-      </c>
-      <c r="D15" s="22" t="s">
-        <v>398</v>
+      <c r="A15" s="30" t="s">
+        <v>354</v>
+      </c>
+      <c r="B15" s="31">
+        <v>0.5</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>355</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>339</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -40143,17 +39885,17 @@
       <c r="J15" s="3"/>
     </row>
     <row r="16" ht="15.0" customHeight="1">
-      <c r="A16" s="23" t="s">
-        <v>399</v>
-      </c>
-      <c r="B16" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>400</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>366</v>
+      <c r="A16" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B16" s="31">
+        <v>3.0</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>357</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -40162,19 +39904,11 @@
       <c r="I16" s="3"/>
       <c r="J16" s="3"/>
     </row>
-    <row r="17" ht="15.0" customHeight="1">
-      <c r="A17" s="23" t="s">
-        <v>401</v>
-      </c>
-      <c r="B17" s="24">
-        <v>3.0</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="D17" s="22" t="s">
-        <v>402</v>
-      </c>
+    <row r="17">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
@@ -40182,42 +39916,49 @@
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
     </row>
-    <row r="18">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+    <row r="18" ht="15.0" customHeight="1">
+      <c r="A18" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="9"/>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="8"/>
+      <c r="A19" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B19" s="33">
+        <f>B4*SQRT(2)</f>
+        <v>33.9411255</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="B20" s="26">
-        <f>B5*SQRT(2)</f>
-        <v>33.9411255</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>339</v>
+      <c r="A20" s="30" t="s">
+        <v>360</v>
+      </c>
+      <c r="B20" s="33">
+        <f>B4*(1+B7)*SQRT(2)-2*B9</f>
+        <v>36.83229432</v>
+      </c>
+      <c r="C20" s="30" t="s">
+        <v>331</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -40228,15 +39969,15 @@
       <c r="J20" s="3"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="B21" s="26">
-        <f>B5*(1+B8)*SQRT(2)-2*B10</f>
-        <v>36.83229432</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>339</v>
+      <c r="A21" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="B21" s="33">
+        <f>B4*(1-B8)*SQRT(2)-2*B9-B10/2</f>
+        <v>26.34701295</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>331</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -40247,16 +39988,14 @@
       <c r="J21" s="3"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="B22" s="26">
-        <f>B5*(1-B9)*SQRT(2)-2*B10-B11/2</f>
-        <v>26.34701295</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>339</v>
-      </c>
+      <c r="A22" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="B22" s="22" t="str">
+        <f>IF(B20&lt;=40,"OK","REVISAR")</f>
+        <v>OK</v>
+      </c>
+      <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -40266,11 +40005,11 @@
       <c r="J22" s="3"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="23" t="s">
-        <v>407</v>
-      </c>
-      <c r="B23" s="20" t="str">
-        <f>IF(B21&lt;=40,"OK","REVISAR")</f>
+      <c r="A23" s="30" t="s">
+        <v>363</v>
+      </c>
+      <c r="B23" s="22" t="str">
+        <f>IF(B21&gt;=15+B16,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
       <c r="C23" s="3"/>
@@ -40283,11 +40022,11 @@
       <c r="J23" s="3"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="B24" s="20" t="str">
-        <f>IF(B22&gt;=15+B17,"OK","REVISAR")</f>
+      <c r="A24" s="30" t="s">
+        <v>364</v>
+      </c>
+      <c r="B24" s="22" t="str">
+        <f>IF(B20+12&lt;=60,"OK","REVISAR")</f>
         <v>OK</v>
       </c>
       <c r="C24" s="3"/>
@@ -40299,14 +40038,9 @@
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
     </row>
-    <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="B25" s="20" t="str">
-        <f>IF(B21+12&lt;=60,"OK","REVISAR")</f>
-        <v>OK</v>
-      </c>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -40316,327 +40050,332 @@
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-    </row>
-    <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="8"/>
-    </row>
-    <row r="28" ht="42.0" customHeight="1">
-      <c r="A28" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>419</v>
+    <row r="26" ht="15.0" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+      <c r="J26" s="9"/>
+    </row>
+    <row r="27" ht="42.0" customHeight="1">
+      <c r="A27" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>373</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="28" ht="15.0" customHeight="1">
+      <c r="A28" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="B28" s="34">
+        <v>12.0</v>
+      </c>
+      <c r="C28" s="34">
+        <v>5.0</v>
+      </c>
+      <c r="D28" s="35">
+        <f t="shared" ref="D28:D32" si="1">C28*(1+$B$12)</f>
+        <v>6</v>
+      </c>
+      <c r="E28" s="36">
+        <f t="shared" ref="E28:E32" si="2">ABS(B28)*C28</f>
+        <v>60</v>
+      </c>
+      <c r="F28" s="37">
+        <v>0.88</v>
+      </c>
+      <c r="G28" s="36">
+        <f t="shared" ref="G28:G32" si="3">E28/F28</f>
+        <v>68.18181818</v>
+      </c>
+      <c r="H28" s="35">
+        <f t="shared" ref="H28:H32" si="4">G28/$B$21</f>
+        <v>2.587838641</v>
+      </c>
+      <c r="I28" s="35">
+        <f t="shared" ref="I28:I32" si="5">MAX($B$15,(D28/(0.048*$B$14^0.44))^(1/0.725)/(1.378*$B$13)*0.0254)</f>
+        <v>3.556129931</v>
+      </c>
+      <c r="J28" s="34" t="s">
+        <v>375</v>
       </c>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
-        <v>230</v>
-      </c>
-      <c r="B29" s="28">
-        <v>12.0</v>
-      </c>
-      <c r="C29" s="28">
+      <c r="A29" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="B29" s="34">
         <v>5.0</v>
       </c>
-      <c r="D29" s="29">
-        <f t="shared" ref="D29:D33" si="1">C29*(1+$B$13)</f>
-        <v>6</v>
-      </c>
-      <c r="E29" s="30">
-        <f t="shared" ref="E29:E33" si="2">ABS(B29)*C29</f>
-        <v>60</v>
-      </c>
-      <c r="F29" s="31">
-        <v>0.88</v>
-      </c>
-      <c r="G29" s="30">
-        <f t="shared" ref="G29:G33" si="3">E29/F29</f>
-        <v>68.18181818</v>
-      </c>
-      <c r="H29" s="29">
-        <f t="shared" ref="H29:H33" si="4">G29/$B$22</f>
-        <v>2.587838641</v>
-      </c>
-      <c r="I29" s="29">
-        <f t="shared" ref="I29:I33" si="5">MAX($B$16,(D29/(0.048*$B$15^0.44))^(1/0.725)/(1.378*$B$14)*0.0254)</f>
-        <v>3.556129931</v>
-      </c>
-      <c r="J29" s="27" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="B30" s="28">
+      <c r="C29" s="34">
         <v>5.0</v>
       </c>
-      <c r="C30" s="28">
-        <v>5.0</v>
-      </c>
-      <c r="D30" s="29">
+      <c r="D29" s="35">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E29" s="36">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F29" s="37">
         <v>0.85</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G29" s="36">
         <f t="shared" si="3"/>
         <v>29.41176471</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H29" s="35">
         <f t="shared" si="4"/>
         <v>1.116322551</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I29" s="35">
         <f t="shared" si="5"/>
         <v>3.556129931</v>
       </c>
-      <c r="J30" s="27" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="B31" s="28">
+      <c r="J29" s="34" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="30" ht="15.0" customHeight="1">
+      <c r="A30" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="B30" s="34">
         <v>3.3</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C30" s="34">
         <v>3.0</v>
       </c>
-      <c r="D31" s="29">
+      <c r="D30" s="35">
         <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E30" s="36">
         <f t="shared" si="2"/>
         <v>9.9</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F30" s="37">
         <v>0.78</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G30" s="36">
         <f t="shared" si="3"/>
         <v>12.69230769</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H30" s="35">
         <f t="shared" si="4"/>
         <v>0.4817361163</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I30" s="35">
         <f t="shared" si="5"/>
         <v>1.75784001</v>
       </c>
-      <c r="J31" s="27" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="B32" s="28">
+      <c r="J30" s="34" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="31" ht="15.0" customHeight="1">
+      <c r="A31" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="B31" s="34">
         <v>-12.0</v>
       </c>
-      <c r="C32" s="28">
+      <c r="C31" s="34">
         <v>1.0</v>
       </c>
-      <c r="D32" s="29">
+      <c r="D31" s="35">
         <f t="shared" si="1"/>
         <v>1.2</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E31" s="36">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F31" s="37">
         <v>0.75</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G31" s="36">
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-      <c r="H32" s="29">
+      <c r="H31" s="35">
         <f t="shared" si="4"/>
         <v>0.6072794678</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I31" s="35">
         <f t="shared" si="5"/>
         <v>0.5</v>
       </c>
-      <c r="J32" s="27" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="27" t="s">
-        <v>422</v>
-      </c>
-      <c r="B33" s="28">
+      <c r="J31" s="34" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="32" ht="15.0" customHeight="1">
+      <c r="A32" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="B32" s="34">
         <v>15.0</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C32" s="34">
         <v>3.0</v>
       </c>
-      <c r="D33" s="29">
+      <c r="D32" s="35">
         <f t="shared" si="1"/>
         <v>3.6</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E32" s="36">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F32" s="37">
         <v>0.85</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G32" s="36">
         <f t="shared" si="3"/>
         <v>52.94117647</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H32" s="35">
         <f t="shared" si="4"/>
         <v>2.009380592</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I32" s="35">
         <f t="shared" si="5"/>
         <v>1.75784001</v>
       </c>
-      <c r="J33" s="27" t="s">
-        <v>423</v>
+      <c r="J32" s="34" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="33" ht="15.0" customHeight="1">
+      <c r="A33" s="22" t="s">
+        <v>379</v>
+      </c>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="23">
+        <f>SUM(E28:E32)</f>
+        <v>151.9</v>
+      </c>
+      <c r="F33" s="38">
+        <f>E33/G33</f>
+        <v>0.8475282361</v>
+      </c>
+      <c r="G33" s="23">
+        <f t="shared" ref="G33:H33" si="6">SUM(G28:G32)</f>
+        <v>179.2270671</v>
+      </c>
+      <c r="H33" s="39">
+        <f t="shared" si="6"/>
+        <v>6.802557368</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="24" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="20" t="s">
-        <v>424</v>
+      <c r="A34" s="30" t="s">
+        <v>381</v>
       </c>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="21">
-        <f>SUM(E29:E33)</f>
-        <v>151.9</v>
-      </c>
-      <c r="F34" s="32">
-        <f>E34/G34</f>
-        <v>0.8475282361</v>
-      </c>
-      <c r="G34" s="21">
-        <f t="shared" ref="G34:H34" si="6">SUM(G29:G33)</f>
-        <v>179.2270671</v>
-      </c>
-      <c r="H34" s="33">
-        <f t="shared" si="6"/>
-        <v>6.802557368</v>
-      </c>
+      <c r="E34" s="23">
+        <f>G33-E33</f>
+        <v>27.32706705</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
       <c r="I34" s="3"/>
-      <c r="J34" s="22" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="23" t="s">
-        <v>426</v>
-      </c>
+      <c r="J34" s="3"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="21">
-        <f>G34-E34</f>
-        <v>27.32706705</v>
-      </c>
+      <c r="E35" s="3"/>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
+    <row r="36" ht="15.0" customHeight="1">
+      <c r="A36" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="B36" s="8"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="8"/>
+      <c r="E36" s="8"/>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="8"/>
+      <c r="I36" s="8"/>
+      <c r="J36" s="9"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="8"/>
+      <c r="A37" s="30" t="s">
+        <v>383</v>
+      </c>
+      <c r="B37" s="39">
+        <f>H33</f>
+        <v>6.802557368</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="B38" s="33">
-        <f>H34</f>
-        <v>6.802557368</v>
+      <c r="A38" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="B38" s="40">
+        <f>B37/(2*B5)/B10*1000000</f>
+        <v>14171.99452</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -40648,12 +40387,12 @@
       <c r="J38" s="3"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="B39" s="34">
-        <f>B38/(2*B6)/B11*1000000</f>
-        <v>14171.99452</v>
+      <c r="A39" s="30" t="s">
+        <v>385</v>
+      </c>
+      <c r="B39" s="23">
+        <f>B37*B11</f>
+        <v>12.24460326</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -40665,12 +40404,12 @@
       <c r="J39" s="3"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="B40" s="21">
-        <f>B38*B12</f>
-        <v>12.24460326</v>
+      <c r="A40" s="30" t="s">
+        <v>386</v>
+      </c>
+      <c r="B40" s="41">
+        <f>B4*B39</f>
+        <v>293.8704783</v>
       </c>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
@@ -40682,12 +40421,12 @@
       <c r="J40" s="3"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="B41" s="35">
-        <f>B5*B40</f>
-        <v>293.8704783</v>
+      <c r="A41" s="30" t="s">
+        <v>387</v>
+      </c>
+      <c r="B41" s="41">
+        <f>B40*(1+B12)</f>
+        <v>352.644574</v>
       </c>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
@@ -40699,12 +40438,12 @@
       <c r="J41" s="3"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="B42" s="35">
-        <f>B41*(1+B13)</f>
-        <v>352.644574</v>
+      <c r="A42" s="30" t="s">
+        <v>388</v>
+      </c>
+      <c r="B42" s="39">
+        <f>B41/B6</f>
+        <v>2.938704783</v>
       </c>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
@@ -40716,12 +40455,12 @@
       <c r="J42" s="3"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="B43" s="33">
-        <f>B42/B7</f>
-        <v>2.938704783</v>
+      <c r="A43" s="30" t="s">
+        <v>389</v>
+      </c>
+      <c r="B43" s="23">
+        <f>B42*1.5</f>
+        <v>4.408057174</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -40733,12 +40472,12 @@
       <c r="J43" s="3"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="B44" s="21">
-        <f>B43*1.5</f>
-        <v>4.408057174</v>
+      <c r="A44" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="B44" s="23">
+        <f>2*B37</f>
+        <v>13.60511474</v>
       </c>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
@@ -40750,12 +40489,12 @@
       <c r="J44" s="3"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="B45" s="21">
-        <f>2*B38</f>
-        <v>13.60511474</v>
+      <c r="A45" s="30" t="s">
+        <v>391</v>
+      </c>
+      <c r="B45" s="23">
+        <f>MAX(B15,(B37*(1+B12)/(0.048*B14^0.44))^(1/0.725)/(1.378*B13)*0.0254)</f>
+        <v>5.437439778</v>
       </c>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
@@ -40766,14 +40505,9 @@
       <c r="I45" s="3"/>
       <c r="J45" s="3"/>
     </row>
-    <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="B46" s="21">
-        <f>MAX(B16,(B38*(1+B13)/(0.048*B15^0.44))^(1/0.725)/(1.378*B14)*0.0254)</f>
-        <v>5.437439778</v>
-      </c>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -40783,22 +40517,22 @@
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-      <c r="J47" s="3"/>
-    </row>
-    <row r="48" ht="30.0" customHeight="1">
-      <c r="A48" s="36" t="s">
-        <v>437</v>
-      </c>
+    <row r="47" ht="30.0" customHeight="1">
+      <c r="A47" s="42" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="3"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
@@ -52212,27 +51946,14 @@
       <c r="I999" s="3"/>
       <c r="J999" s="3"/>
     </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="3"/>
-      <c r="B1000" s="3"/>
-      <c r="C1000" s="3"/>
-      <c r="D1000" s="3"/>
-      <c r="E1000" s="3"/>
-      <c r="F1000" s="3"/>
-      <c r="G1000" s="3"/>
-      <c r="H1000" s="3"/>
-      <c r="I1000" s="3"/>
-      <c r="J1000" s="3"/>
-    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A27:J27"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A47:J47"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
